--- a/outputs/daily/hr_rankings_2026-08-13.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-13.xlsx
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>59.7</v>
+        <v>59.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>74.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>78</v>
       </c>
       <c r="U46" t="n">
-        <v>48.3</v>
+        <v>46.5</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
@@ -45220,7 +45220,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>80</v>
       </c>
       <c r="U163" t="n">
-        <v>12</v>
+        <v>10.1</v>
       </c>
       <c r="V163" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
@@ -45324,7 +45324,7 @@
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
@@ -46650,7 +46650,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>59.7</v>
+        <v>59.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>74.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -46739,12 +46739,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-13.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-13.xlsx
@@ -5266,34 +5266,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6102,34 +6098,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11678,34 +11670,30 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21360,28 +21348,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y76" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22478,34 +22470,30 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -28326,34 +28314,30 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -30278,34 +30262,30 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36382,34 +36362,30 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -40824,28 +40800,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W146" t="inlineStr"/>
-      <c r="X146" t="inlineStr"/>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y146" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -50576,34 +50556,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -51412,34 +51388,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-13.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-13.xlsx
@@ -10038,34 +10038,30 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10602,34 +10598,30 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12566,34 +12558,30 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19514,34 +19502,30 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -23688,28 +23672,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -29258,34 +29246,30 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -35102,34 +35086,30 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -37898,34 +37878,30 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41788,28 +41764,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W149" t="inlineStr"/>
-      <c r="X149" t="inlineStr"/>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y149" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-13.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-13.xlsx
@@ -2687,27 +2687,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>680664</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luis García Jr.</t>
+          <t>Eduardo Valencia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-13T17:35:00Z</t>
+          <t>2026-08-13T17:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2722,21 +2722,21 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2750,26 +2750,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.6</v>
+        <v>84.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.5</v>
+        <v>20.2</v>
       </c>
       <c r="R9" t="n">
-        <v>80.7</v>
+        <v>47.6</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>33.7</v>
+        <v>32</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Contact streak: 6/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 19.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.4% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2851,112 +2851,112 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.8473</t>
+          <t>103.2988</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4924</t>
+          <t>0.634</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2065</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3908</t>
+          <t>0.3463</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1191</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -2967,27 +2967,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>680664</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eduardo Valencia</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13T17:10:00Z</t>
+          <t>2026-08-13T17:35:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3002,21 +3002,21 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>61.8</v>
+        <v>61.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3030,26 +3030,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>84.5</v>
+        <v>49.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>20.2</v>
+        <v>50.5</v>
       </c>
       <c r="R10" t="n">
-        <v>47.6</v>
+        <v>80.7</v>
       </c>
       <c r="S10" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>32</v>
+        <v>8.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 6/18 over last 7 games</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.4% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 19.3 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3131,112 +3131,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.11</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.2988</t>
+          <t>101.8473</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>0.4924</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.2065</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>21.91</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3463</t>
+          <t>0.3908</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1191</t>
+          <t>0.1645</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -5195,47 +5195,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806146</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>George Lombard Jr.</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-13T17:35:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5258,61 +5258,65 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>36.4</v>
+        <v>52.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>50.5</v>
+        <v>54.8</v>
       </c>
       <c r="R18" t="n">
-        <v>80.7</v>
+        <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>66.7</v>
+        <v>74.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5329,27 +5333,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 19.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5359,112 +5363,104 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.1434</t>
+          <t>102.0873</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.4624</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2091</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>44.38</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.1965</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3908</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.31</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.42</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -5475,47 +5471,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>699013</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Esmerlyn Valdez</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-13T17:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5524,7 +5520,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5538,65 +5534,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>52.5</v>
+        <v>72.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>54.8</v>
+        <v>41.3</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>35</v>
       </c>
       <c r="S19" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>74.5</v>
+        <v>7</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5613,134 +5605,142 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>102.0873</t>
+          <t>102.7111</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4624</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.2091</t>
+          <t>0.263</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>35.1</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>0.317</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>7.13</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
           <t>44.38</t>
         </is>
       </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>31.57</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>27.38</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>18.2</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.1965</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>10.68</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>43.51</t>
-        </is>
-      </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.4099</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>28.42</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+          <t>25.24</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -5751,22 +5751,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>699013</t>
+          <t>682829</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Esmerlyn Valdez</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5781,17 +5781,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5814,26 +5814,26 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>72.8</v>
+        <v>55.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>41.3</v>
+        <v>42.7</v>
       </c>
       <c r="R20" t="n">
-        <v>35</v>
+        <v>38.6</v>
       </c>
       <c r="S20" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T20" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U20" t="n">
-        <v>7</v>
+        <v>36.7</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5868,7 +5868,7 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -5890,137 +5890,137 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 10.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>102.7111</t>
+          <t>104.0239</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.4618</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>0.1968</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.24</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>53.07</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.2089</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4099</t>
+          <t>0.4321</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6031,22 +6031,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>682829</t>
+          <t>664040</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6061,17 +6061,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>56</v>
+        <v>55.8</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6098,22 +6098,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>55.6</v>
+        <v>52.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.7</v>
+        <v>41.3</v>
       </c>
       <c r="R21" t="n">
-        <v>38.6</v>
+        <v>35</v>
       </c>
       <c r="S21" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>36.7</v>
+        <v>44.8</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6185,122 +6185,122 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.6% barrel, 13.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>45.62</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>91.03</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>104.0239</t>
+          <t>101.4653</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4618</t>
+          <t>0.4521</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1968</t>
+          <t>0.2058</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>75.24</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>53.07</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>46.86</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.2089</t>
+          <t>0.2266</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.38</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4321</t>
+          <t>0.4099</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6311,47 +6311,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>664040</t>
+          <t>621439</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Byron Buxton</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-13T17:10:00Z</t>
+          <t>2026-08-13T23:30:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6374,58 +6374,62 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>52.2</v>
+        <v>67.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>41.3</v>
+        <v>50.3</v>
       </c>
       <c r="R22" t="n">
-        <v>35</v>
+        <v>27.6</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>88.7</v>
       </c>
       <c r="T22" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U22" t="n">
-        <v>45.9</v>
+        <v>6</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6450,22 +6454,22 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.7% barrel, 25.7 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6475,112 +6479,104 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>91.03</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>101.4653</t>
+          <t>102.324</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4521</t>
+          <t>0.5112</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.2058</t>
+          <t>0.2611</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.3486</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>74.37</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>43.88</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.2266</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>88.91</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4099</t>
+          <t>0.4233</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>25.24</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>27.88</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Field of Dreams</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6591,56 +6587,56 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>621439</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Byron Buxton</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-13T23:30:00Z</t>
+          <t>2026-08-13T17:10:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>671096</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>55.8</v>
+        <v>55.3</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6654,62 +6650,58 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>67.8</v>
+        <v>54</v>
       </c>
       <c r="Q23" t="n">
-        <v>50.3</v>
+        <v>40.2</v>
       </c>
       <c r="R23" t="n">
-        <v>27.6</v>
+        <v>38.6</v>
       </c>
       <c r="S23" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>30.3</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6729,7 +6721,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -6739,124 +6731,132 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.7% barrel, 25.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>102.324</t>
+          <t>100.4804</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.5112</t>
+          <t>0.4812</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.2611</t>
+          <t>0.2277</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.3486</t>
+          <t>0.3624</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>74.37</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>43.88</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.2828</t>
+          <t>0.216</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>88.91</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.4233</t>
+          <t>0.4081</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1583</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>27.88</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr"/>
-      <c r="BH23" t="inlineStr"/>
+          <t>27.86</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Field of Dreams</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6867,27 +6867,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>806146</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-13T17:10:00Z</t>
+          <t>2026-08-13T17:35:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6897,26 +6897,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>671096</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>55.4</v>
+        <v>55.1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6930,26 +6930,26 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>54</v>
+        <v>36.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>40.2</v>
+        <v>50.5</v>
       </c>
       <c r="R24" t="n">
-        <v>38.6</v>
+        <v>80.7</v>
       </c>
       <c r="S24" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U24" t="n">
-        <v>31.6</v>
+        <v>46</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -6984,7 +6984,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -7001,12 +7001,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -7016,127 +7016,127 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Last 7 games: 7/23, 1 HR</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 17.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 19.3 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>100.4804</t>
+          <t>99.1434</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.4812</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.2277</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3624</t>
+          <t>0.373</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.4081</t>
+          <t>0.3908</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.1583</t>
+          <t>0.1645</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>54.5</v>
+        <v>54.8</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>78</v>
       </c>
       <c r="U26" t="n">
-        <v>32</v>
+        <v>38.3</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Contact streak: 5/15 over last 7 games</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>686527</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Julio Rodríguez</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8874,11 +8874,11 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>46.7</v>
+        <v>58.3</v>
       </c>
       <c r="Q31" t="n">
         <v>9.4</v>
@@ -8887,13 +8887,13 @@
         <v>80.7</v>
       </c>
       <c r="S31" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T31" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>52.8</v>
+        <v>37.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -8945,27 +8945,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.0% barrel, 4.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.0% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -8975,67 +8975,67 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.81</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>102.7139</t>
+          <t>102.6606</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.4734</t>
+          <t>0.5106</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.1978</t>
+          <t>0.2325</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3503</t>
+          <t>0.3669</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>74.22</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>67.06</t>
+          <t>44.37</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>40.11</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1818</t>
+          <t>0.223</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>686527</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9154,11 +9154,11 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>58.3</v>
+        <v>46.7</v>
       </c>
       <c r="Q32" t="n">
         <v>9.4</v>
@@ -9167,13 +9167,13 @@
         <v>80.7</v>
       </c>
       <c r="S32" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U32" t="n">
-        <v>33.7</v>
+        <v>52.8</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9225,27 +9225,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.0% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.0% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9255,67 +9255,67 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.57</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>91.81</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>102.6606</t>
+          <t>102.7139</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.5106</t>
+          <t>0.4734</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.2325</t>
+          <t>0.1978</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3669</t>
+          <t>0.3503</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>74.22</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>44.37</t>
+          <t>67.06</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>40.11</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.33</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>59.3</v>
+        <v>57.2</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Contact streak: 11/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
@@ -10491,27 +10491,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>663886</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-13T17:35:00Z</t>
+          <t>2026-08-13T17:10:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -10526,21 +10526,21 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Max Fried</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>608331</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10554,26 +10554,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>54.7</v>
+        <v>52.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.9</v>
+        <v>44.1</v>
       </c>
       <c r="R37" t="n">
-        <v>80.7</v>
+        <v>38.6</v>
       </c>
       <c r="S37" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T37" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>4.5</v>
+        <v>21.8</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10630,137 +10630,137 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 3/21, 1 HR</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.0% barrel, 4.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.99</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>100.7197</t>
+          <t>100.6041</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.4231</t>
+          <t>0.4522</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.2096</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3382</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>74.99</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>52.67</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>53.94</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.2006</t>
+          <t>0.1697</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>32.51</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.2835</t>
+          <t>0.4321</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.0795</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10771,27 +10771,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>663886</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-13T17:10:00Z</t>
+          <t>2026-08-13T17:35:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -10806,21 +10806,21 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Max Fried</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>608331</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>52.5</v>
+        <v>52.3</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10834,26 +10834,26 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>52.3</v>
+        <v>54.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>44.1</v>
+        <v>8.9</v>
       </c>
       <c r="R38" t="n">
-        <v>38.6</v>
+        <v>80.7</v>
       </c>
       <c r="S38" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T38" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U38" t="n">
-        <v>21.8</v>
+        <v>0</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10905,142 +10905,142 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 1 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.0% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>90.99</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>100.6041</t>
+          <t>100.7197</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.4522</t>
+          <t>0.4231</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.2096</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.3382</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>74.99</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>52.67</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>53.94</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.1697</t>
+          <t>0.2006</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>32.51</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>0.4321</t>
+          <t>0.2835</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0795</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr"/>
@@ -22208,7 +22208,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>80</v>
       </c>
       <c r="U79" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 0 HR</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
@@ -22439,22 +22439,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>804668</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rafael Flores Jr.</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -22469,22 +22469,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>671096</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -22502,26 +22502,26 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>56.5</v>
+        <v>13.1</v>
       </c>
       <c r="Q80" t="n">
-        <v>41.3</v>
+        <v>40.2</v>
       </c>
       <c r="R80" t="n">
-        <v>35</v>
+        <v>38.6</v>
       </c>
       <c r="S80" t="n">
-        <v>44.8</v>
+        <v>93.2</v>
       </c>
       <c r="T80" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
@@ -22573,142 +22573,142 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/14, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>91.16</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>100.4927</t>
+          <t>97.4428</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>0.4734</t>
+          <t>0.3351</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>0.2248</t>
+          <t>0.0947</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.3722</t>
+          <t>0.2965</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>73.61</t>
+          <t>67.19</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>50.17</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1153</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>0.4099</t>
+          <t>0.4081</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1583</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr"/>
@@ -22719,22 +22719,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>804668</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Rafael Flores Jr.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -22749,26 +22749,26 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>671096</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -22782,26 +22782,26 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>13.1</v>
+        <v>56.5</v>
       </c>
       <c r="Q81" t="n">
-        <v>40.2</v>
+        <v>41.3</v>
       </c>
       <c r="R81" t="n">
-        <v>38.6</v>
+        <v>35</v>
       </c>
       <c r="S81" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T81" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U81" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -22853,142 +22853,142 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 1/14, 0 HR</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 17.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>45.98</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>91.16</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>97.4428</t>
+          <t>100.4927</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>0.3351</t>
+          <t>0.4734</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>0.0947</t>
+          <t>0.2248</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.2965</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>67.19</t>
+          <t>73.61</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>50.17</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.1153</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>44.38</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>0.4081</t>
+          <t>0.4099</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>0.1583</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr"/>
@@ -30852,7 +30852,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>80</v>
       </c>
       <c r="U110" t="n">
-        <v>53.9</v>
+        <v>52.1</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -30952,7 +30952,7 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
@@ -39423,47 +39423,47 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>665923</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-13T17:10:00Z</t>
+          <t>2026-08-13T23:30:00Z</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Braxton Ashcraft</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>677952</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -39472,7 +39472,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -39486,58 +39486,62 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P141" t="n">
-        <v>21.7</v>
+        <v>10.9</v>
       </c>
       <c r="Q141" t="n">
-        <v>32.1</v>
+        <v>50.3</v>
       </c>
       <c r="R141" t="n">
-        <v>35</v>
+        <v>27.6</v>
       </c>
       <c r="S141" t="n">
-        <v>44.8</v>
+        <v>59.8</v>
       </c>
       <c r="T141" t="n">
         <v>50</v>
       </c>
       <c r="U141" t="n">
-        <v>60.3</v>
+        <v>21.1</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W141" t="inlineStr">
+      <c r="Z141" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC141" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39557,27 +39561,27 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Contact streak: 4/10 over last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.1% barrel, 14.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.7% barrel, 25.7 HR allowed</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
@@ -39587,112 +39591,104 @@
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.08</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>96.3175</t>
+          <t>96.5828</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>0.3454</t>
+          <t>0.3528</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>0.2959</t>
+          <t>0.3128</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>71.38</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>45.43</t>
+          <t>39.03</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>26.83</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>0.2067</t>
+          <t>0.1094</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>88.91</t>
         </is>
       </c>
       <c r="BD141" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.4233</t>
         </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>24.83</t>
-        </is>
-      </c>
-      <c r="BG141" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH141" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>27.88</t>
+        </is>
+      </c>
+      <c r="BG141" t="inlineStr"/>
+      <c r="BH141" t="inlineStr"/>
       <c r="BI141" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Field of Dreams</t>
         </is>
       </c>
       <c r="BJ141" t="inlineStr"/>
@@ -39703,47 +39699,47 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>665923</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-13T23:30:00Z</t>
+          <t>2026-08-13T17:10:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Braxton Ashcraft</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>677952</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -39752,7 +39748,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -39766,62 +39762,58 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>10.9</v>
+        <v>21.7</v>
       </c>
       <c r="Q142" t="n">
-        <v>50.3</v>
+        <v>32.1</v>
       </c>
       <c r="R142" t="n">
-        <v>27.6</v>
+        <v>35</v>
       </c>
       <c r="S142" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T142" t="n">
         <v>50</v>
       </c>
       <c r="U142" t="n">
-        <v>21.1</v>
+        <v>54.9</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39841,27 +39833,27 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Contact streak: 4/11 over last 7 games</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.7% barrel, 25.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.1% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -39871,104 +39863,112 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>96.5828</t>
+          <t>96.3175</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.3528</t>
+          <t>0.3454</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.1083</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.3128</t>
+          <t>0.2959</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>71.38</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>39.03</t>
+          <t>45.43</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>26.83</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.1094</t>
+          <t>0.2067</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>88.91</t>
+          <t>89.26</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.4233</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>27.88</t>
-        </is>
-      </c>
-      <c r="BG142" t="inlineStr"/>
-      <c r="BH142" t="inlineStr"/>
+          <t>24.83</t>
+        </is>
+      </c>
+      <c r="BG142" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH142" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Field of Dreams</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr"/>
@@ -42475,12 +42475,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>701162</t>
+          <t>595879</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ben Malgeri</t>
+          <t>Javier Báez</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -42505,7 +42505,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -42542,7 +42542,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>16.2</v>
+        <v>12.9</v>
       </c>
       <c r="Q152" t="n">
         <v>20.2</v>
@@ -42551,13 +42551,13 @@
         <v>47.6</v>
       </c>
       <c r="S152" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T152" t="n">
         <v>78</v>
       </c>
       <c r="U152" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -42592,7 +42592,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
@@ -42609,22 +42609,22 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/12, 1 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
@@ -42639,67 +42639,67 @@
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.17</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>99.2365</t>
+          <t>97.2926</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0.0898</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2745</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>41.41</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.1126</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
@@ -42755,12 +42755,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>595879</t>
+          <t>701162</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Javier Báez</t>
+          <t>Ben Malgeri</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -42785,7 +42785,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -42804,7 +42804,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>12.9</v>
+        <v>16.2</v>
       </c>
       <c r="Q153" t="n">
         <v>20.2</v>
@@ -42831,13 +42831,13 @@
         <v>47.6</v>
       </c>
       <c r="S153" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T153" t="n">
         <v>78</v>
       </c>
       <c r="U153" t="n">
-        <v>21.1</v>
+        <v>25.3</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -42872,7 +42872,7 @@
       <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr"/>
@@ -42889,22 +42889,22 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 2/12, 1 HR</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
@@ -42919,67 +42919,67 @@
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>86.17</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>97.2926</t>
+          <t>99.2365</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>0.3394</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>0.0898</t>
+          <t>0.082</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.2745</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>0.1126</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
@@ -48085,27 +48085,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>680664</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luis García Jr.</t>
+          <t>Eduardo Valencia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-13T17:35:00Z</t>
+          <t>2026-08-13T17:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -48120,21 +48120,21 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -48148,26 +48148,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.6</v>
+        <v>84.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.5</v>
+        <v>20.2</v>
       </c>
       <c r="R9" t="n">
-        <v>80.7</v>
+        <v>47.6</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>33.7</v>
+        <v>32</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -48224,22 +48224,22 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Contact streak: 6/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 19.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.4% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -48249,112 +48249,112 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.8473</t>
+          <t>103.2988</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4924</t>
+          <t>0.634</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2065</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3908</t>
+          <t>0.3463</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1191</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -48365,27 +48365,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>680664</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eduardo Valencia</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13T17:10:00Z</t>
+          <t>2026-08-13T17:35:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -48400,21 +48400,21 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>61.8</v>
+        <v>61.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -48428,26 +48428,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>84.5</v>
+        <v>49.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>20.2</v>
+        <v>50.5</v>
       </c>
       <c r="R10" t="n">
-        <v>47.6</v>
+        <v>80.7</v>
       </c>
       <c r="S10" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>32</v>
+        <v>8.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -48499,12 +48499,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -48514,12 +48514,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 6/18 over last 7 games</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.4% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 19.3 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -48529,112 +48529,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.11</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.2988</t>
+          <t>101.8473</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>0.4924</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.2065</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>21.91</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3463</t>
+          <t>0.3908</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1191</t>
+          <t>0.1645</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -50593,47 +50593,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806146</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>George Lombard Jr.</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-13T17:35:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -50656,61 +50656,65 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>36.4</v>
+        <v>52.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>50.5</v>
+        <v>54.8</v>
       </c>
       <c r="R18" t="n">
-        <v>80.7</v>
+        <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>66.7</v>
+        <v>74.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -50727,27 +50731,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 19.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -50757,112 +50761,104 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.1434</t>
+          <t>102.0873</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.4624</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2091</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>44.38</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.1965</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3908</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.31</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.42</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -50873,47 +50869,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>699013</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Esmerlyn Valdez</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-13T17:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -50922,7 +50918,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -50936,65 +50932,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>52.5</v>
+        <v>72.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>54.8</v>
+        <v>41.3</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>35</v>
       </c>
       <c r="S19" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>74.5</v>
+        <v>7</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -51011,134 +51003,142 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>102.0873</t>
+          <t>102.7111</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4624</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.2091</t>
+          <t>0.263</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>35.1</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>0.317</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>7.13</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
           <t>44.38</t>
         </is>
       </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>31.57</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>27.38</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>18.2</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.1965</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>10.68</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>43.51</t>
-        </is>
-      </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.4099</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>28.42</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+          <t>25.24</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -51149,22 +51149,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>699013</t>
+          <t>682829</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Esmerlyn Valdez</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -51179,17 +51179,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -51198,7 +51198,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -51212,26 +51212,26 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>72.8</v>
+        <v>55.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>41.3</v>
+        <v>42.7</v>
       </c>
       <c r="R20" t="n">
-        <v>35</v>
+        <v>38.6</v>
       </c>
       <c r="S20" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T20" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U20" t="n">
-        <v>7</v>
+        <v>36.7</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -51245,7 +51245,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -51266,7 +51266,7 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -51288,137 +51288,137 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 10.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.96</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>102.7111</t>
+          <t>104.0239</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.4618</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>0.1968</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.24</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>53.07</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.2089</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4099</t>
+          <t>0.4321</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -51429,22 +51429,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>682829</t>
+          <t>664040</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -51459,17 +51459,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -51478,7 +51478,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>56</v>
+        <v>55.8</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -51496,22 +51496,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>55.6</v>
+        <v>52.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.7</v>
+        <v>41.3</v>
       </c>
       <c r="R21" t="n">
-        <v>38.6</v>
+        <v>35</v>
       </c>
       <c r="S21" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>36.7</v>
+        <v>44.8</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -51563,12 +51563,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -51583,122 +51583,122 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.6% barrel, 13.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>45.62</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>91.03</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>104.0239</t>
+          <t>101.4653</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4618</t>
+          <t>0.4521</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1968</t>
+          <t>0.2058</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>75.24</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>53.07</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>46.86</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.2089</t>
+          <t>0.2266</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.38</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4321</t>
+          <t>0.4099</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-13.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-13.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>65</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>35.4</v>
       </c>
       <c r="R2" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64.3</v>
+        <v>62.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>54.8</v>
       </c>
       <c r="R3" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1632,11 +1632,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>60.2</v>
+        <v>58.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Longshot</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1656,7 +1656,7 @@
         <v>54.8</v>
       </c>
       <c r="R5" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>58.9</v>
+        <v>57.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>54.8</v>
       </c>
       <c r="R6" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>57.7</v>
+        <v>56.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>54.8</v>
       </c>
       <c r="R7" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2711,27 +2711,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>53.3</v>
+        <v>52.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2774,26 +2774,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.7</v>
+        <v>50.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.8</v>
+        <v>13.5</v>
       </c>
       <c r="R9" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S9" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>36</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2849,127 +2849,127 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.01</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.8281</t>
+          <t>102.1801</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3928</t>
+          <t>0.475</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.3553</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1572</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -2995,24 +2995,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>694208</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Moisés Ballesteros</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-14T02:07:00Z</t>
@@ -3025,17 +3025,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.4</v>
+        <v>51.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3058,26 +3058,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>50.4</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.5</v>
+        <v>50.8</v>
       </c>
       <c r="R10" t="n">
         <v>56.7</v>
       </c>
       <c r="S10" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>70.59999999999999</v>
+        <v>7</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3133,127 +3133,127 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>102.1801</t>
+          <t>101.0984</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1478</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3553</t>
+          <t>0.3207</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.92</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>0.1431</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -3279,27 +3279,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>642350</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3309,26 +3309,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3342,61 +3342,57 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36.2</v>
+        <v>52</v>
       </c>
       <c r="Q11" t="n">
-        <v>35.4</v>
+        <v>50.8</v>
       </c>
       <c r="R11" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3413,12 +3409,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3428,112 +3424,112 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 5/17, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>99.849</t>
+          <t>100.2971</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4336</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.2071</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.289</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.29</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1855</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -3548,7 +3544,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3559,27 +3555,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>694208</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Moisés Ballesteros</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3589,17 +3585,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3626,22 +3622,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>36.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>50.8</v>
+        <v>54.8</v>
       </c>
       <c r="R12" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S12" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3655,7 +3651,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3675,7 +3671,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -3697,27 +3693,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3727,112 +3723,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>89.01</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>101.0984</t>
+          <t>100.8281</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3979</t>
+          <t>0.3928</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3207</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1431</t>
+          <t>0.1572</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3843,24 +3839,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>642350</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-14T02:07:00Z</t>
@@ -3873,17 +3869,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3892,7 +3888,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>51.9</v>
+        <v>51.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3906,37 +3902,45 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>52</v>
+        <v>50.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>50.8</v>
+        <v>13.5</v>
       </c>
       <c r="R13" t="n">
         <v>56.7</v>
       </c>
       <c r="S13" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>44.5</v>
+        <v>56.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -3951,12 +3955,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3973,127 +3977,127 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.2971</t>
+          <t>102.0363</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.4441</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2071</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>0.3451</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>73.29</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>41.99</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.2254</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -4119,27 +4123,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4149,26 +4153,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4182,26 +4186,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>50.1</v>
+        <v>36.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.5</v>
+        <v>35.4</v>
       </c>
       <c r="R14" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S14" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U14" t="n">
-        <v>56.2</v>
+        <v>46.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4210,34 +4214,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4257,27 +4257,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4287,112 +4287,112 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>102.0363</t>
+          <t>99.849</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4441</t>
+          <t>0.4336</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1985</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3451</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2254</t>
+          <t>0.1855</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>54.8</v>
       </c>
       <c r="R15" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4687,27 +4687,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>666139</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4717,26 +4717,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>49.7</v>
+        <v>48.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4754,22 +4754,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41.4</v>
+        <v>34.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>35.4</v>
+        <v>50.8</v>
       </c>
       <c r="R16" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S16" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4778,33 +4778,37 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4826,7 +4830,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4836,12 +4840,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4851,97 +4855,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>38.83</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.8738</t>
+          <t>99.4278</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4221</t>
+          <t>0.3868</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1404</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -4956,7 +4960,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -4967,12 +4971,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4997,7 +5001,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5016,7 +5020,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>49.6</v>
+        <v>48.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5030,26 +5034,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>42.4</v>
+        <v>41.4</v>
       </c>
       <c r="Q17" t="n">
         <v>35.4</v>
       </c>
       <c r="R17" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S17" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5063,7 +5067,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5101,12 +5105,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5116,12 +5120,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5131,67 +5135,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.4673</t>
+          <t>100.8738</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4824</t>
+          <t>0.4221</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1923</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3689</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>30.01</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5226,12 +5230,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5247,12 +5251,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>666139</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5277,7 +5281,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5296,7 +5300,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5310,11 +5314,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>34.6</v>
+        <v>28</v>
       </c>
       <c r="Q18" t="n">
         <v>50.8</v>
@@ -5323,13 +5327,13 @@
         <v>56.7</v>
       </c>
       <c r="S18" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5343,7 +5347,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5363,12 +5367,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5385,12 +5389,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5400,12 +5404,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5415,67 +5419,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.4278</t>
+          <t>99.3512</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3868</t>
+          <t>0.394</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1404</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5531,27 +5535,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5566,17 +5570,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -5598,13 +5602,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>42.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>50.8</v>
+        <v>35.4</v>
       </c>
       <c r="R19" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S19" t="n">
         <v>94.90000000000001</v>
@@ -5613,7 +5617,7 @@
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5622,37 +5626,33 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5684,12 +5684,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5699,112 +5699,112 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.3512</t>
+          <t>100.4673</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.4824</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1923</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.3689</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -5815,27 +5815,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>48.1</v>
+        <v>47.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5878,26 +5878,26 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>36.7</v>
+        <v>13.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>54.8</v>
+        <v>50.8</v>
       </c>
       <c r="R20" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S20" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U20" t="n">
-        <v>18.3</v>
+        <v>28.9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5983,97 +5983,97 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>87.43</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.4213</t>
+          <t>97.0663</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.3852</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3294</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>73.27</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1173</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6099,27 +6099,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>694384</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6129,17 +6129,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>47.4</v>
+        <v>46.7</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6162,26 +6162,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>13.6</v>
+        <v>36.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.8</v>
+        <v>54.8</v>
       </c>
       <c r="R21" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S21" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T21" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>28.9</v>
+        <v>18.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6267,112 +6267,112 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>87.43</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>97.0663</t>
+          <t>101.4213</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3852</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3294</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1173</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6667,27 +6667,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>694203</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6697,26 +6697,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>45.3</v>
+        <v>44.8</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6730,26 +6730,26 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>23.7</v>
+        <v>25.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>34.4</v>
+        <v>50.8</v>
       </c>
       <c r="R23" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S23" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T23" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U23" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6758,33 +6758,37 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -6801,12 +6805,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -6816,12 +6820,12 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 2/11, 0 HR</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -6831,97 +6835,97 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.81</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>99.655</t>
+          <t>98.3737</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.3886</t>
+          <t>0.3321</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1183</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.3196</t>
+          <t>0.2574</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>73.36</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.1367</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
@@ -6936,7 +6940,7 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6947,27 +6951,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>694203</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6977,26 +6981,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>44.8</v>
+        <v>43.9</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -7010,26 +7014,26 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>25.7</v>
+        <v>23.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>50.8</v>
+        <v>34.4</v>
       </c>
       <c r="R24" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S24" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U24" t="n">
-        <v>9.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -7038,37 +7042,33 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/11, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7115,112 +7115,112 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>98.3737</t>
+          <t>99.655</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.3321</t>
+          <t>0.3886</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.1183</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.2574</t>
+          <t>0.3196</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>73.36</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.1367</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -7231,27 +7231,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>571771</t>
+          <t>694671</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enrique Hernández</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7261,26 +7261,26 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>44.4</v>
+        <v>43.5</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7294,23 +7294,23 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="R25" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S25" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T25" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -7322,30 +7322,34 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7365,12 +7369,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -7380,12 +7384,12 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/12, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7395,97 +7399,97 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>89.93</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>99.5161</t>
+          <t>100.7005</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.4164</t>
+          <t>0.4088</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.1744</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.3024</t>
+          <t>0.3152</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>70.47</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>42.19</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.2155</t>
+          <t>0.2054</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
@@ -7500,7 +7504,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7511,27 +7515,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>694671</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7541,26 +7545,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>43.5</v>
+        <v>42.9</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7574,23 +7578,23 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>40.2</v>
+        <v>39.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>13.5</v>
+        <v>35.4</v>
       </c>
       <c r="R26" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T26" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -7602,34 +7606,30 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -7679,112 +7679,112 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>89.93</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>100.7005</t>
+          <t>99.5161</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4088</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.1744</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3152</t>
+          <t>0.3024</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>70.47</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.2054</t>
+          <t>0.2155</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>42.9</v>
+        <v>41.5</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>35.4</v>
       </c>
       <c r="R27" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S27" t="n">
         <v>64.3</v>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8124,7 +8124,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>42.5</v>
+        <v>41.1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>35.4</v>
       </c>
       <c r="R28" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S28" t="n">
         <v>76.2</v>
@@ -8334,12 +8334,12 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>39.6</v>
+        <v>38.1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>54.8</v>
       </c>
       <c r="R29" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S29" t="n">
         <v>52.4</v>
@@ -8618,12 +8618,12 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>54.8</v>
       </c>
       <c r="R30" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S30" t="n">
         <v>44.8</v>
@@ -8902,12 +8902,12 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>35.4</v>
       </c>
       <c r="R37" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S37" t="n">
         <v>44.8</v>
@@ -10862,12 +10862,12 @@
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
@@ -11258,7 +11258,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>65</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>35.4</v>
       </c>
       <c r="R2" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -11468,12 +11468,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64.3</v>
+        <v>62.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>54.8</v>
       </c>
       <c r="R3" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -11752,12 +11752,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -12106,11 +12106,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>60.2</v>
+        <v>58.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Longshot</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -12130,7 +12130,7 @@
         <v>54.8</v>
       </c>
       <c r="R5" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -12320,12 +12320,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -12390,7 +12390,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>58.9</v>
+        <v>57.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>54.8</v>
       </c>
       <c r="R6" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -12674,7 +12674,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>57.7</v>
+        <v>56.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>54.8</v>
       </c>
       <c r="R7" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -12880,12 +12880,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -13185,27 +13185,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13215,17 +13215,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -13234,7 +13234,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>53.3</v>
+        <v>52.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -13248,26 +13248,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.7</v>
+        <v>50.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.8</v>
+        <v>13.5</v>
       </c>
       <c r="R9" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S9" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>36</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -13323,127 +13323,127 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.01</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.8281</t>
+          <t>102.1801</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3928</t>
+          <t>0.475</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.3553</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1572</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -13469,24 +13469,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>694208</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Moisés Ballesteros</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-14T02:07:00Z</t>
@@ -13499,17 +13499,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.4</v>
+        <v>51.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13532,26 +13532,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>50.4</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.5</v>
+        <v>50.8</v>
       </c>
       <c r="R10" t="n">
         <v>56.7</v>
       </c>
       <c r="S10" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>70.59999999999999</v>
+        <v>7</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -13585,12 +13585,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -13607,127 +13607,127 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>102.1801</t>
+          <t>101.0984</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1478</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3553</t>
+          <t>0.3207</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.92</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>0.1431</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -13753,27 +13753,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>642350</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -13783,26 +13783,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13816,61 +13816,57 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36.2</v>
+        <v>52</v>
       </c>
       <c r="Q11" t="n">
-        <v>35.4</v>
+        <v>50.8</v>
       </c>
       <c r="R11" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -13887,12 +13883,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -13902,112 +13898,112 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 5/17, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>99.849</t>
+          <t>100.2971</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4336</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.2071</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.289</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.29</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1855</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -14022,7 +14018,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -14033,27 +14029,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>694208</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Moisés Ballesteros</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -14063,17 +14059,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14100,22 +14096,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>36.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>50.8</v>
+        <v>54.8</v>
       </c>
       <c r="R12" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S12" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -14129,7 +14125,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -14149,7 +14145,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -14171,27 +14167,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -14201,112 +14197,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>89.01</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>101.0984</t>
+          <t>100.8281</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3979</t>
+          <t>0.3928</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3207</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1431</t>
+          <t>0.1572</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -14317,24 +14313,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>642350</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-14T02:07:00Z</t>
@@ -14347,17 +14343,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14366,7 +14362,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>51.9</v>
+        <v>51.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14380,37 +14376,45 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>52</v>
+        <v>50.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>50.8</v>
+        <v>13.5</v>
       </c>
       <c r="R13" t="n">
         <v>56.7</v>
       </c>
       <c r="S13" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>44.5</v>
+        <v>56.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -14425,12 +14429,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -14447,127 +14451,127 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.2971</t>
+          <t>102.0363</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.4441</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2071</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>0.3451</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>73.29</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>41.99</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.2254</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -14593,27 +14597,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -14623,26 +14627,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -14656,26 +14660,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>50.1</v>
+        <v>36.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.5</v>
+        <v>35.4</v>
       </c>
       <c r="R14" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S14" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U14" t="n">
-        <v>56.2</v>
+        <v>46.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -14684,34 +14688,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -14731,27 +14731,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -14761,112 +14761,112 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>102.0363</t>
+          <t>99.849</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4441</t>
+          <t>0.4336</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1985</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3451</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2254</t>
+          <t>0.1855</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -14926,7 +14926,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>54.8</v>
       </c>
       <c r="R15" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -15140,12 +15140,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -15161,27 +15161,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>666139</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -15191,26 +15191,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>49.7</v>
+        <v>48.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15228,22 +15228,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41.4</v>
+        <v>34.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>35.4</v>
+        <v>50.8</v>
       </c>
       <c r="R16" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S16" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -15252,33 +15252,37 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -15300,7 +15304,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -15310,12 +15314,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -15325,97 +15329,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>38.83</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.8738</t>
+          <t>99.4278</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4221</t>
+          <t>0.3868</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1404</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -15430,7 +15434,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -15441,12 +15445,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15471,7 +15475,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -15490,7 +15494,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>49.6</v>
+        <v>48.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15504,26 +15508,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>42.4</v>
+        <v>41.4</v>
       </c>
       <c r="Q17" t="n">
         <v>35.4</v>
       </c>
       <c r="R17" t="n">
-        <v>56.1</v>
+        <v>46.6</v>
       </c>
       <c r="S17" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -15537,7 +15541,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -15575,12 +15579,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -15590,12 +15594,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -15605,67 +15609,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.4673</t>
+          <t>100.8738</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4824</t>
+          <t>0.4221</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1923</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3689</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>30.01</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -15700,12 +15704,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -15721,12 +15725,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>666139</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15751,7 +15755,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -15770,7 +15774,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -15784,11 +15788,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>34.6</v>
+        <v>28</v>
       </c>
       <c r="Q18" t="n">
         <v>50.8</v>
@@ -15797,13 +15801,13 @@
         <v>56.7</v>
       </c>
       <c r="S18" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -15817,7 +15821,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -15837,12 +15841,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -15859,12 +15863,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -15874,12 +15878,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -15889,67 +15893,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.4278</t>
+          <t>99.3512</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3868</t>
+          <t>0.394</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1404</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -16005,27 +16009,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -16040,17 +16044,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -16072,13 +16076,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>42.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>50.8</v>
+        <v>35.4</v>
       </c>
       <c r="R19" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S19" t="n">
         <v>94.90000000000001</v>
@@ -16087,7 +16091,7 @@
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -16096,37 +16100,33 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -16143,12 +16143,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -16158,12 +16158,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -16173,112 +16173,112 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.3512</t>
+          <t>100.4673</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.4824</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1923</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.3689</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -16289,27 +16289,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>48.1</v>
+        <v>47.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16352,26 +16352,26 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>36.7</v>
+        <v>13.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>54.8</v>
+        <v>50.8</v>
       </c>
       <c r="R20" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="S20" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U20" t="n">
-        <v>18.3</v>
+        <v>28.9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -16442,12 +16442,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -16457,97 +16457,97 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>87.43</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.4213</t>
+          <t>97.0663</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.3852</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3294</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>73.27</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.06</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1173</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -16573,27 +16573,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>694384</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -16603,17 +16603,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -16622,7 +16622,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>47.4</v>
+        <v>46.7</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16636,26 +16636,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>13.6</v>
+        <v>36.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.8</v>
+        <v>54.8</v>
       </c>
       <c r="R21" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="S21" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T21" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>28.9</v>
+        <v>18.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -16711,12 +16711,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -16726,12 +16726,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -16741,112 +16741,112 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>87.43</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>97.0663</t>
+          <t>101.4213</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3852</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3294</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1173</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
